--- a/output/Data and Chart Outputs/global_lng_liquefaction_capacity.xlsx
+++ b/output/Data and Chart Outputs/global_lng_liquefaction_capacity.xlsx
@@ -3730,7 +3730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3741,7 +3741,6 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3785,11 +3784,6 @@
           <t>result</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
-        <is>
-          <t>release_date</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3827,12 +3821,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NEW/CHANGED - parsed</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
+          <t>UNCHANGED (same SHA-256) - stored parse reused</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3878,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>FIRST SEEN</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3913,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FIRST SEEN</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3948,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>FIRST SEEN</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3968,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ee363ea67ce7eb565ae64d8f614e5398bc6496572abeb90bef162874096e1129</t>
+          <t>47c40967a9d203e226af5d7fee07f483e5af695daf9c55a2492e8da731a2a027</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3989,7 +3978,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>FIRST SEEN</t>
+          <t>CHANGED - re-read the document and update the curated rows</t>
         </is>
       </c>
     </row>
@@ -4006,16 +3995,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>"6203d-65da2d598c64a-gzip"</t>
+          <t>W/"6203c-65da391a334c8-gzip"</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mon, 12 Oct 2026 11:16:49 GMT</t>
+          <t>Mon, 12 Oct 2026 12:09:24 GMT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>36781</v>
+        <v>36779</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -4024,7 +4013,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>FIRST SEEN</t>
+          <t>CHANGED - re-read the document and update the curated rows</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4048,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>FIRST SEEN</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4083,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>FIRST SEEN</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -4114,7 +4103,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>7c0b68510b8462f12ddf4eb4f46638ab41f7abc57e8652e8d2b70fa347fbf4c0</t>
+          <t>f0c80a20d57bc16c9bada2c03007c4375a8ac65cfc9b23f2207a6db17ee282c5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4124,7 +4113,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>FIRST SEEN</t>
+          <t>CHANGED - re-read the document and update the curated rows</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4130,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mon, 12 Oct 2026 00:05:19 GMT</t>
+          <t>Mon, 12 Oct 2026 12:09:27 GMT</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4151,7 +4140,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>FIRST SEEN</t>
+          <t>CHANGED - re-read the document and update the curated rows</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4170,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>FIRST SEEN</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4205,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>FIRST SEEN</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4235,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>FIRST SEEN</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4265,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>FIRST SEEN</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4295,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>FIRST SEEN</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4315,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>68061fb2da55d5d73fb292f68f0449ef109866098c5bf68b2d13a700fb45d224</t>
+          <t>7ad2e185977a54ddb84cdef2f9760d14bbcb2c502cbd68449e32c8e685719272</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4336,7 +4325,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>FIRST SEEN</t>
+          <t>CHANGED - re-read the document and update the curated rows</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4352,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>FIRST SEEN</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -6708,11 +6697,6 @@
       <c r="B43" t="inlineStr">
         <is>
           <t>Lake Charles LNG (additional DOE application)</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>n/a</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -42694,7 +42678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -42728,6 +42712,295 @@
       <c r="E1" s="5" t="inlineStr">
         <is>
           <t>date_seen</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Global supply|United States|Cameron LNG Train 4A</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>expected_online</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Global supply|United States|Lake Charles LNG</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>expected_online</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Global supply|United States|Woodside Louisiana LNG (formerly Driftwood LNG) Phase 2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>expected_online</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Global supply|United States|Freeport LNG Train 4C</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>expected_online</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Global supply|United States|Texas LNG</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>expected_online</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Global supply|United States|Gulf LNGE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>expected_online</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Global supply|United States|Delfin FLNG additional vessels (beyond Train 1)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>expected_online</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Global supply|United States|Alaska LNG</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>expected_online</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Global supply|Qatar|North Field East expansion, Trains 2-4 (3 x 8 mtpa)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>expected_online</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Global supply|Qatar|North Field South expansion (2 trains x 8 mtpa)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>expected_online</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Global supply|Qatar|North Field West expansion (2 trains x 8 mtpa)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>expected_online</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Global supply|Canada|LNG Canada Phase 2 (2 trains, +14 mtpa)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>expected_online</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Global supply|Canada|Ksi Lisims LNG (floating, 12 mtpa)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>expected_online</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Global supply|Russia|Arctic LNG 2, Train 3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>expected_online</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Global supply|Nigeria|Nigeria LNG Train 7</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>expected_online</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Global supply|Indonesia|Abadi LNG (Masela)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>expected_online</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Global supply|United States|Sabine Pass Stage 5 expansion (Train 7 + BOG re-liquefaction)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>expected_online</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/global_lng_liquefaction_capacity.xlsx
+++ b/output/Data and Chart Outputs/global_lng_liquefaction_capacity.xlsx
@@ -3836,6 +3836,19 @@
           <t>https://www.industry.gov.au/sites/default/files/2026-10/resources-and-energy-quarterly-september-2026.pdf</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>"6abedf5d-579419"</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Thu, 01 Oct 2026 22:31:57 GMT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5739545</v>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -3843,7 +3856,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>UNREACHABLE (ReadTimeout)</t>
+          <t>CHANGED - re-read the document and update the curated rows</t>
         </is>
       </c>
     </row>
@@ -3966,11 +3979,6 @@
       <c r="E7" t="n">
         <v>78242</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>47c40967a9d203e226af5d7fee07f483e5af695daf9c55a2492e8da731a2a027</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -3978,7 +3986,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CHANGED - re-read the document and update the curated rows</t>
+          <t>UNCHANGED (key phrase still present)</t>
         </is>
       </c>
     </row>
@@ -3993,18 +4001,8 @@
           <t>https://www.eni.com/en-IT/media/press-release/2025/10/pr-eni-announces-final-investment-decision-mozambique-coral-north-project.html</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>W/"6203c-65da391a334c8-gzip"</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Mon, 12 Oct 2026 12:09:24 GMT</t>
-        </is>
-      </c>
       <c r="E8" t="n">
-        <v>36779</v>
+        <v>401469</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -4013,7 +4011,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>CHANGED - re-read the document and update the curated rows</t>
+          <t>UNCHANGED (key phrase still present)</t>
         </is>
       </c>
     </row>
@@ -4101,11 +4099,6 @@
       <c r="E11" t="n">
         <v>119417</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>f0c80a20d57bc16c9bada2c03007c4375a8ac65cfc9b23f2207a6db17ee282c5</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -4113,7 +4106,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CHANGED - re-read the document and update the curated rows</t>
+          <t>UNCHANGED (key phrase still present)</t>
         </is>
       </c>
     </row>
@@ -4128,10 +4121,8 @@
           <t>https://mozambiquelng.co.mz/about-the-mozambique-liquefied-natural-gas-project/development/</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Mon, 12 Oct 2026 12:09:27 GMT</t>
-        </is>
+      <c r="E12" t="n">
+        <v>108698</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -4140,7 +4131,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CHANGED - re-read the document and update the curated rows</t>
+          <t>CHANGED - key phrase '13.12 MTPA' not found: re-read the document and update the curated rows</t>
         </is>
       </c>
     </row>
@@ -4158,11 +4149,6 @@
       <c r="E13" t="n">
         <v>300145</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>fd6c274108f3abcb0eda2f9054c84702684daaa03cacecd6c33274eedd490298</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -4170,7 +4156,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>UNCHANGED (key phrase still present)</t>
         </is>
       </c>
     </row>
@@ -4313,11 +4299,6 @@
       <c r="E18" t="n">
         <v>319744</v>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>7ad2e185977a54ddb84cdef2f9760d14bbcb2c502cbd68449e32c8e685719272</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -4325,7 +4306,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>CHANGED - re-read the document and update the curated rows</t>
+          <t>UNCHANGED (key phrase still present)</t>
         </is>
       </c>
     </row>
@@ -4340,10 +4321,8 @@
           <t>https://boereport.com/2026/10/07/qatarenergys-lng-expansion-project-poised-to-start-operations-in-november-sources-say/amp/</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Mon, 12 Oct 2026 11:50:15 GMT</t>
-        </is>
+      <c r="E19" t="n">
+        <v>61350</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -4352,14 +4331,14 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>UNCHANGED (key phrase still present)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DISR REQ listing</t>
+          <t>DISR Resources and Energy Quarterly: newest edition in the listing</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4374,7 +4353,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>UNREACHABLE (ReadTimeout)</t>
+          <t>newest listed: june-2026; curated rows use september-2026 - NEW EDITION: re-read section 6 LNG and the nameplate map</t>
         </is>
       </c>
     </row>
@@ -42678,7 +42657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -42712,295 +42691,6 @@
       <c r="E1" s="5" t="inlineStr">
         <is>
           <t>date_seen</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Global supply|United States|Cameron LNG Train 4A</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>expected_online</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Global supply|United States|Lake Charles LNG</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>expected_online</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Global supply|United States|Woodside Louisiana LNG (formerly Driftwood LNG) Phase 2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>expected_online</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Global supply|United States|Freeport LNG Train 4C</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>expected_online</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Global supply|United States|Texas LNG</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>expected_online</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Global supply|United States|Gulf LNGE</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>expected_online</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Global supply|United States|Delfin FLNG additional vessels (beyond Train 1)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>expected_online</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Global supply|United States|Alaska LNG</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>expected_online</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Global supply|Qatar|North Field East expansion, Trains 2-4 (3 x 8 mtpa)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>expected_online</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Global supply|Qatar|North Field South expansion (2 trains x 8 mtpa)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>expected_online</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Global supply|Qatar|North Field West expansion (2 trains x 8 mtpa)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>expected_online</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Global supply|Canada|LNG Canada Phase 2 (2 trains, +14 mtpa)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>expected_online</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Global supply|Canada|Ksi Lisims LNG (floating, 12 mtpa)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>expected_online</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Global supply|Russia|Arctic LNG 2, Train 3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>expected_online</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Global supply|Nigeria|Nigeria LNG Train 7</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>expected_online</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Global supply|Indonesia|Abadi LNG (Masela)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>expected_online</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Global supply|United States|Sabine Pass Stage 5 expansion (Train 7 + BOG re-liquefaction)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>expected_online</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/global_lng_liquefaction_capacity.xlsx
+++ b/output/Data and Chart Outputs/global_lng_liquefaction_capacity.xlsx
@@ -2121,12 +2121,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Project page: development (two liquefaction units, 13.12 MTPA)</t>
+          <t>Project page (two liquefaction units, 13.12 MTPA)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://mozambiquelng.co.mz/about-the-mozambique-liquefied-natural-gas-project/development/</t>
+          <t>https://www.mozambiquelng.co.mz/about-the-mozambique-liquefied-natural-gas-project/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CHANGED - re-read the document and update the curated rows</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>401469</v>
+        <v>401468</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -4113,16 +4113,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mozambique LNG (TotalEnergies-operated project site): Project page: development (two liquefaction units, 13.12 MTPA)</t>
+          <t>Mozambique LNG (TotalEnergies-operated project site): Project page (two liquefaction units, 13.12 MTPA)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://mozambiquelng.co.mz/about-the-mozambique-liquefied-natural-gas-project/development/</t>
+          <t>https://www.mozambiquelng.co.mz/about-the-mozambique-liquefied-natural-gas-project/</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>108698</v>
+        <v>106525</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CHANGED - key phrase '13.12 MTPA' not found: re-read the document and update the curated rows</t>
+          <t>FIRST SEEN (key phrase present)</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DISR Resources and Energy Quarterly: newest edition in the listing</t>
+          <t>DISR Resources and Energy Quarterly: newest edition (next editions probed by address)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>newest listed: june-2026; curated rows use september-2026 - NEW EDITION: re-read section 6 LNG and the nameplate map</t>
+          <t>newest found: september-2026; curated rows use september-2026</t>
         </is>
       </c>
     </row>
@@ -40574,12 +40574,12 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>Project page: development (two liquefaction units, 13.12 MTPA)</t>
+          <t>Project page (two liquefaction units, 13.12 MTPA)</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>https://mozambiquelng.co.mz/about-the-mozambique-liquefied-natural-gas-project/development/</t>
+          <t>https://www.mozambiquelng.co.mz/about-the-mozambique-liquefied-natural-gas-project/</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">

--- a/output/Data and Chart Outputs/global_lng_liquefaction_capacity.xlsx
+++ b/output/Data and Chart Outputs/global_lng_liquefaction_capacity.xlsx
@@ -3816,7 +3816,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -3977,11 +3977,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>78242</v>
+        <v>78241</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -4002,11 +4002,11 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>401468</v>
+        <v>401173</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -4028,25 +4028,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>"8b769b-gjNnKhPc9L1uQPS6FP/AZDKctG0"</t>
+          <t>"15a06e7-MjahPzUa0rsMOLQwe1mYIHMfyi8"</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Wed, 10 Jun 2026 08:53:56 GMT</t>
+          <t>Fri, 23 Oct 2026 14:50:49 GMT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>9139867</v>
+        <v>22677223</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>CHANGED - re-read the document and update the curated rows</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -4097,11 +4097,11 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>119417</v>
+        <v>119075</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>FIRST SEEN (key phrase present)</t>
+          <t>UNCHANGED (key phrase still present)</t>
         </is>
       </c>
     </row>
@@ -4147,11 +4147,11 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>300145</v>
+        <v>300144</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -4322,11 +4322,11 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>61350</v>
+        <v>61300</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -31145,7 +31145,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -31243,7 +31243,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -31341,7 +31341,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -31439,7 +31439,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -31537,7 +31537,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -31733,7 +31733,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -31831,7 +31831,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -31929,7 +31929,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -32027,7 +32027,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -32125,7 +32125,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -32223,7 +32223,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -32321,7 +32321,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -32419,7 +32419,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -32517,7 +32517,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -32615,7 +32615,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -32713,7 +32713,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -32811,7 +32811,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -32909,7 +32909,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -33007,7 +33007,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -33105,7 +33105,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -33203,7 +33203,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -33301,7 +33301,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -33399,7 +33399,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -33497,7 +33497,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -33595,7 +33595,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -33693,7 +33693,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -33791,7 +33791,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -33889,7 +33889,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -33987,7 +33987,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -34085,7 +34085,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -34183,7 +34183,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -34281,7 +34281,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -34379,7 +34379,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -34477,7 +34477,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -34575,7 +34575,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -34673,7 +34673,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -34771,7 +34771,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -34869,7 +34869,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -34967,7 +34967,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -35065,7 +35065,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -35163,7 +35163,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -35261,7 +35261,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -35359,7 +35359,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -35457,7 +35457,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -35550,7 +35550,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -35643,7 +35643,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -35736,7 +35736,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -35829,7 +35829,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -35922,7 +35922,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -36015,7 +36015,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -36108,7 +36108,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -36201,7 +36201,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -36299,7 +36299,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -36397,7 +36397,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -36495,7 +36495,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -36588,7 +36588,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -36681,7 +36681,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -36774,7 +36774,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -36872,7 +36872,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -36970,7 +36970,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -37063,7 +37063,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -37161,7 +37161,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -37253,7 +37253,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -37346,7 +37346,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -37444,7 +37444,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -37640,7 +37640,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -37738,7 +37738,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -37836,7 +37836,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -37934,7 +37934,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -38032,7 +38032,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -38130,7 +38130,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -38228,7 +38228,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -38326,7 +38326,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -38424,7 +38424,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -38522,7 +38522,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -38620,7 +38620,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -38712,7 +38712,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -38810,7 +38810,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -38908,7 +38908,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -39006,7 +39006,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -39104,7 +39104,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -39202,7 +39202,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -39300,7 +39300,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -39393,7 +39393,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -39491,7 +39491,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -39584,7 +39584,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -39682,7 +39682,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -39780,7 +39780,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -39878,7 +39878,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -39976,7 +39976,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -40074,7 +40074,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -40172,7 +40172,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -40270,7 +40270,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -40368,7 +40368,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -40466,7 +40466,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -40564,7 +40564,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -40662,7 +40662,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -40760,7 +40760,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -40858,7 +40858,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -40956,7 +40956,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -41054,7 +41054,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -41152,7 +41152,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -41250,7 +41250,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -41348,7 +41348,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -41446,7 +41446,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -41544,7 +41544,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -41642,7 +41642,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -41740,7 +41740,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -41838,7 +41838,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -41936,7 +41936,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -42034,7 +42034,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -42127,7 +42127,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -42225,7 +42225,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -42323,7 +42323,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -42421,7 +42421,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -42612,7 +42612,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
